--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124078504</v>
+        <v>124081020</v>
       </c>
       <c r="B2" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548404</v>
+        <v>548463</v>
       </c>
       <c r="R2" t="n">
-        <v>6828910</v>
+        <v>6828933</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,6 +765,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,11 +780,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -779,14 +788,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081020</v>
+        <v>124080834</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -821,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548463</v>
+        <v>548475</v>
       </c>
       <c r="R3" t="n">
-        <v>6828933</v>
+        <v>6828937</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,11 +885,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,17 +903,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081277</v>
+        <v>124080853</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,35 +922,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548355</v>
+        <v>548478</v>
       </c>
       <c r="R4" t="n">
-        <v>6828975</v>
+        <v>6828941</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,6 +1010,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080746</v>
+        <v>124081035</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1051,12 +1064,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548458</v>
+        <v>548469</v>
       </c>
       <c r="R5" t="n">
-        <v>6828939</v>
+        <v>6828955</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,17 +1137,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124081065</v>
+        <v>124078504</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,35 +1160,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548456</v>
+        <v>548404</v>
       </c>
       <c r="R6" t="n">
-        <v>6828959</v>
+        <v>6828910</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,6 +1235,11 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1239,14 +1248,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080853</v>
+        <v>124080746</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1281,19 +1290,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548478</v>
+        <v>548458</v>
       </c>
       <c r="R7" t="n">
-        <v>6828941</v>
+        <v>6828939</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1358,14 +1363,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124081035</v>
+        <v>124080625</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1398,16 +1403,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1417,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R8" t="n">
-        <v>6828955</v>
+        <v>6829001</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1452,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1473,17 +1475,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124080834</v>
+        <v>124081277</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,39 +1494,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1532,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548475</v>
+        <v>548355</v>
       </c>
       <c r="R9" t="n">
-        <v>6828937</v>
+        <v>6828975</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,7 +1574,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1595,7 +1592,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124080625</v>
+        <v>124081065</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1628,8 +1625,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1639,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548416</v>
+        <v>548456</v>
       </c>
       <c r="R10" t="n">
-        <v>6829001</v>
+        <v>6828959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1677,11 +1682,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081020</v>
+        <v>124080746</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548463</v>
+        <v>548458</v>
       </c>
       <c r="R2" t="n">
-        <v>6828933</v>
+        <v>6828939</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,11 +765,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -903,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080853</v>
+        <v>124081277</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,43 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548478</v>
+        <v>548355</v>
       </c>
       <c r="R4" t="n">
-        <v>6828941</v>
+        <v>6828975</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081035</v>
+        <v>124078504</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,35 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548469</v>
+        <v>548404</v>
       </c>
       <c r="R5" t="n">
-        <v>6828955</v>
+        <v>6828910</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,6 +1106,11 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1137,17 +1119,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124078504</v>
+        <v>124080853</v>
       </c>
       <c r="B6" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,26 +1142,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548404</v>
+        <v>548478</v>
       </c>
       <c r="R6" t="n">
-        <v>6828910</v>
+        <v>6828941</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,11 +1230,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1248,14 +1238,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080746</v>
+        <v>124080625</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1288,16 +1278,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1307,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548458</v>
+        <v>548416</v>
       </c>
       <c r="R7" t="n">
-        <v>6828939</v>
+        <v>6829001</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,6 +1327,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1363,14 +1350,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080625</v>
+        <v>124081065</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1403,8 +1390,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548416</v>
+        <v>548456</v>
       </c>
       <c r="R8" t="n">
-        <v>6829001</v>
+        <v>6828959</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,11 +1447,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1475,17 +1465,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081277</v>
+        <v>124081035</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,35 +1484,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548355</v>
+        <v>548469</v>
       </c>
       <c r="R9" t="n">
-        <v>6828975</v>
+        <v>6828955</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1574,6 +1568,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081065</v>
+        <v>124081020</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1627,12 +1622,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1644,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548456</v>
+        <v>548463</v>
       </c>
       <c r="R10" t="n">
-        <v>6828959</v>
+        <v>6828933</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1677,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124078504</v>
+        <v>124080834</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548404</v>
+        <v>548475</v>
       </c>
       <c r="R2" t="n">
-        <v>6828910</v>
+        <v>6828937</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,11 +775,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -779,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081277</v>
+        <v>124080746</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548355</v>
+        <v>548458</v>
       </c>
       <c r="R3" t="n">
-        <v>6828975</v>
+        <v>6828939</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081065</v>
+        <v>124081035</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -931,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548456</v>
+        <v>548469</v>
       </c>
       <c r="R4" t="n">
-        <v>6828959</v>
+        <v>6828955</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080746</v>
+        <v>124081277</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,39 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548458</v>
+        <v>548355</v>
       </c>
       <c r="R5" t="n">
-        <v>6828939</v>
+        <v>6828975</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1112,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124080834</v>
+        <v>124080625</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1159,16 +1163,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1178,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548475</v>
+        <v>548416</v>
       </c>
       <c r="R6" t="n">
-        <v>6828937</v>
+        <v>6829001</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,6 +1212,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1234,14 +1235,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080625</v>
+        <v>124081065</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1274,8 +1275,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1285,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548416</v>
+        <v>548456</v>
       </c>
       <c r="R7" t="n">
-        <v>6829001</v>
+        <v>6828959</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,11 +1332,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,17 +1350,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124081020</v>
+        <v>124078504</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,35 +1373,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548463</v>
+        <v>548404</v>
       </c>
       <c r="R8" t="n">
-        <v>6828933</v>
+        <v>6828910</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,11 +1438,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,6 +1448,11 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1466,14 +1461,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124080853</v>
+        <v>124081020</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1508,19 +1503,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548478</v>
+        <v>548463</v>
       </c>
       <c r="R9" t="n">
-        <v>6828941</v>
+        <v>6828933</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,6 +1556,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081035</v>
+        <v>124080853</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1627,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1635,7 +1631,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548469</v>
+        <v>548478</v>
       </c>
       <c r="R10" t="n">
-        <v>6828955</v>
+        <v>6828941</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124229699</v>
+        <v>124230620</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548469</v>
+        <v>548414</v>
       </c>
       <c r="R11" t="n">
-        <v>6828940</v>
+        <v>6828951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230620</v>
+        <v>124230968</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548414</v>
+        <v>548416</v>
       </c>
       <c r="R12" t="n">
-        <v>6828951</v>
+        <v>6828945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230968</v>
+        <v>124229699</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548416</v>
+        <v>548469</v>
       </c>
       <c r="R13" t="n">
-        <v>6828945</v>
+        <v>6828940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,11 +2047,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080834</v>
+        <v>124081277</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548475</v>
+        <v>548355</v>
       </c>
       <c r="R2" t="n">
-        <v>6828937</v>
+        <v>6828975</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080746</v>
+        <v>124081035</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +820,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548458</v>
+        <v>548469</v>
       </c>
       <c r="R3" t="n">
-        <v>6828939</v>
+        <v>6828955</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081035</v>
+        <v>124080746</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +935,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548469</v>
+        <v>548458</v>
       </c>
       <c r="R4" t="n">
-        <v>6828955</v>
+        <v>6828939</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081277</v>
+        <v>124080625</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1027,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548355</v>
+        <v>548416</v>
       </c>
       <c r="R5" t="n">
-        <v>6828975</v>
+        <v>6829001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,12 +1097,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,17 +1120,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124080625</v>
+        <v>124078504</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,27 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548416</v>
+        <v>548404</v>
       </c>
       <c r="R6" t="n">
-        <v>6829001</v>
+        <v>6828910</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,11 +1208,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1226,6 +1217,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1242,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081065</v>
+        <v>124081020</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1277,12 +1273,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1294,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548456</v>
+        <v>548463</v>
       </c>
       <c r="R7" t="n">
-        <v>6828959</v>
+        <v>6828933</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,6 +1326,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124078504</v>
+        <v>124080834</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,26 +1374,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548404</v>
+        <v>548475</v>
       </c>
       <c r="R8" t="n">
-        <v>6828910</v>
+        <v>6828937</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,11 +1458,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1461,14 +1466,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081020</v>
+        <v>124081065</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,12 +1508,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1520,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548463</v>
+        <v>548456</v>
       </c>
       <c r="R9" t="n">
-        <v>6828933</v>
+        <v>6828959</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1556,11 +1561,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1831,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230968</v>
+        <v>124229699</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548416</v>
+        <v>548469</v>
       </c>
       <c r="R12" t="n">
-        <v>6828945</v>
+        <v>6828940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,11 +1923,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124229699</v>
+        <v>124230178</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1990,12 +1985,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548469</v>
+        <v>548465</v>
       </c>
       <c r="R13" t="n">
-        <v>6828940</v>
+        <v>6828959</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,6 +2042,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230178</v>
+        <v>124230968</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548465</v>
+        <v>548416</v>
       </c>
       <c r="R14" t="n">
-        <v>6828959</v>
+        <v>6828945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081035</v>
+        <v>124080853</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -828,7 +828,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548469</v>
+        <v>548478</v>
       </c>
       <c r="R3" t="n">
-        <v>6828955</v>
+        <v>6828941</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080746</v>
+        <v>124080834</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -935,12 +939,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -952,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548458</v>
+        <v>548475</v>
       </c>
       <c r="R4" t="n">
-        <v>6828939</v>
+        <v>6828937</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1127,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124078504</v>
+        <v>124081035</v>
       </c>
       <c r="B6" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,26 +1147,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548404</v>
+        <v>548469</v>
       </c>
       <c r="R6" t="n">
-        <v>6828910</v>
+        <v>6828955</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,11 +1231,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1231,14 +1239,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081020</v>
+        <v>124081065</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1273,12 +1281,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1290,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548463</v>
+        <v>548456</v>
       </c>
       <c r="R7" t="n">
-        <v>6828933</v>
+        <v>6828959</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,11 +1334,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080834</v>
+        <v>124080746</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1393,12 +1396,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1410,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548475</v>
+        <v>548458</v>
       </c>
       <c r="R8" t="n">
-        <v>6828937</v>
+        <v>6828939</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081065</v>
+        <v>124078504</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,35 +1492,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1525,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548456</v>
+        <v>548404</v>
       </c>
       <c r="R9" t="n">
-        <v>6828959</v>
+        <v>6828910</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,6 +1567,11 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1581,14 +1580,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124080853</v>
+        <v>124081020</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1623,19 +1622,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548478</v>
+        <v>548463</v>
       </c>
       <c r="R10" t="n">
-        <v>6828941</v>
+        <v>6828933</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,6 +1675,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230620</v>
+        <v>124229699</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548414</v>
+        <v>548469</v>
       </c>
       <c r="R11" t="n">
-        <v>6828951</v>
+        <v>6828940</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,11 +1799,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124229699</v>
+        <v>124230178</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1866,12 +1861,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548469</v>
+        <v>548465</v>
       </c>
       <c r="R12" t="n">
-        <v>6828940</v>
+        <v>6828959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,6 +1918,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230178</v>
+        <v>124230620</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548465</v>
+        <v>548414</v>
       </c>
       <c r="R13" t="n">
-        <v>6828959</v>
+        <v>6828951</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081277</v>
+        <v>124080834</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548355</v>
+        <v>548475</v>
       </c>
       <c r="R2" t="n">
-        <v>6828975</v>
+        <v>6828937</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080853</v>
+        <v>124078504</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548478</v>
+        <v>548404</v>
       </c>
       <c r="R3" t="n">
-        <v>6828941</v>
+        <v>6828910</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,6 +881,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -897,14 +894,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080834</v>
+        <v>124081035</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -956,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548475</v>
+        <v>548469</v>
       </c>
       <c r="R4" t="n">
-        <v>6828937</v>
+        <v>6828955</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,17 +1009,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080625</v>
+        <v>124081277</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,31 +1028,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548416</v>
+        <v>548355</v>
       </c>
       <c r="R5" t="n">
-        <v>6829001</v>
+        <v>6828975</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,18 +1102,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,14 +1119,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124081035</v>
+        <v>124081020</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1166,12 +1161,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548469</v>
+        <v>548463</v>
       </c>
       <c r="R6" t="n">
-        <v>6828955</v>
+        <v>6828933</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,6 +1216,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,14 +1239,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081065</v>
+        <v>124080625</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1279,16 +1279,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1298,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548456</v>
+        <v>548416</v>
       </c>
       <c r="R7" t="n">
-        <v>6828959</v>
+        <v>6829001</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,6 +1328,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1354,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1476,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124078504</v>
+        <v>124080853</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,26 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548404</v>
+        <v>548478</v>
       </c>
       <c r="R9" t="n">
-        <v>6828910</v>
+        <v>6828941</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,11 +1577,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1580,14 +1585,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081020</v>
+        <v>124081065</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1622,12 +1627,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1639,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548463</v>
+        <v>548456</v>
       </c>
       <c r="R10" t="n">
-        <v>6828933</v>
+        <v>6828959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1675,11 +1680,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230178</v>
+        <v>124230620</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548465</v>
+        <v>548414</v>
       </c>
       <c r="R12" t="n">
-        <v>6828959</v>
+        <v>6828951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230620</v>
+        <v>124230968</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548414</v>
+        <v>548416</v>
       </c>
       <c r="R13" t="n">
-        <v>6828951</v>
+        <v>6828945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230968</v>
+        <v>124230178</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548416</v>
+        <v>548465</v>
       </c>
       <c r="R14" t="n">
-        <v>6828945</v>
+        <v>6828959</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080834</v>
+        <v>124081035</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548475</v>
+        <v>548469</v>
       </c>
       <c r="R2" t="n">
-        <v>6828937</v>
+        <v>6828955</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124078504</v>
+        <v>124081020</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +806,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548404</v>
+        <v>548463</v>
       </c>
       <c r="R3" t="n">
-        <v>6828910</v>
+        <v>6828933</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,6 +880,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,11 +895,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -894,14 +903,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081035</v>
+        <v>124080625</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -934,16 +943,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -953,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R4" t="n">
-        <v>6828955</v>
+        <v>6829001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +992,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1009,7 +1015,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1126,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124081020</v>
+        <v>124080746</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1161,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1178,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548463</v>
+        <v>548458</v>
       </c>
       <c r="R6" t="n">
-        <v>6828933</v>
+        <v>6828939</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,11 +1222,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,14 +1240,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080625</v>
+        <v>124080853</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1279,9 +1280,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548416</v>
+        <v>548478</v>
       </c>
       <c r="R7" t="n">
-        <v>6829001</v>
+        <v>6828941</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,11 +1341,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,17 +1359,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080746</v>
+        <v>124078504</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,35 +1382,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1410,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548458</v>
+        <v>548404</v>
       </c>
       <c r="R8" t="n">
-        <v>6828939</v>
+        <v>6828910</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,6 +1457,11 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1466,14 +1470,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124080853</v>
+        <v>124080834</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1508,7 +1512,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1516,11 +1520,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548478</v>
+        <v>548475</v>
       </c>
       <c r="R9" t="n">
-        <v>6828941</v>
+        <v>6828937</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124229699</v>
+        <v>124230968</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R11" t="n">
-        <v>6828940</v>
+        <v>6828945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230968</v>
+        <v>124230178</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1985,12 +1990,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548416</v>
+        <v>548465</v>
       </c>
       <c r="R13" t="n">
-        <v>6828945</v>
+        <v>6828959</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2051,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230178</v>
+        <v>124229699</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2109,12 +2114,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2130,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548465</v>
+        <v>548469</v>
       </c>
       <c r="R14" t="n">
-        <v>6828959</v>
+        <v>6828940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,11 +2171,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081035</v>
+        <v>124080746</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548469</v>
+        <v>548458</v>
       </c>
       <c r="R2" t="n">
-        <v>6828955</v>
+        <v>6828939</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081020</v>
+        <v>124081065</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548463</v>
+        <v>548456</v>
       </c>
       <c r="R3" t="n">
-        <v>6828933</v>
+        <v>6828959</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080625</v>
+        <v>124081035</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -943,8 +938,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -954,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548416</v>
+        <v>548469</v>
       </c>
       <c r="R4" t="n">
-        <v>6829001</v>
+        <v>6828955</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,11 +995,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,17 +1013,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081277</v>
+        <v>124080853</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1032,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548355</v>
+        <v>548478</v>
       </c>
       <c r="R5" t="n">
-        <v>6828975</v>
+        <v>6828941</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,6 +1120,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124080746</v>
+        <v>124080625</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1165,16 +1172,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548458</v>
+        <v>548416</v>
       </c>
       <c r="R6" t="n">
-        <v>6828939</v>
+        <v>6829001</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,6 +1221,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1240,17 +1244,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124080853</v>
+        <v>124078504</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,39 +1267,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548478</v>
+        <v>548404</v>
       </c>
       <c r="R7" t="n">
-        <v>6828941</v>
+        <v>6828910</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,6 +1342,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1359,17 +1355,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124078504</v>
+        <v>124080834</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,26 +1378,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548404</v>
+        <v>548475</v>
       </c>
       <c r="R8" t="n">
-        <v>6828910</v>
+        <v>6828937</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,11 +1462,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124080834</v>
+        <v>124081020</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548475</v>
+        <v>548463</v>
       </c>
       <c r="R9" t="n">
-        <v>6828937</v>
+        <v>6828933</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,6 +1565,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081065</v>
+        <v>124081277</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,39 +1609,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1644,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548456</v>
+        <v>548355</v>
       </c>
       <c r="R10" t="n">
-        <v>6828959</v>
+        <v>6828975</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230968</v>
+        <v>124230620</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548416</v>
+        <v>548414</v>
       </c>
       <c r="R11" t="n">
-        <v>6828945</v>
+        <v>6828951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230620</v>
+        <v>124230178</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548414</v>
+        <v>548465</v>
       </c>
       <c r="R12" t="n">
-        <v>6828951</v>
+        <v>6828959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230178</v>
+        <v>124229699</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548465</v>
+        <v>548469</v>
       </c>
       <c r="R13" t="n">
-        <v>6828959</v>
+        <v>6828940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,11 +2047,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124229699</v>
+        <v>124230968</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2135,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R14" t="n">
-        <v>6828940</v>
+        <v>6828945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,6 +2166,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080746</v>
+        <v>124080853</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,15 +710,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548458</v>
+        <v>548478</v>
       </c>
       <c r="R2" t="n">
-        <v>6828939</v>
+        <v>6828941</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081065</v>
+        <v>124081020</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +829,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548456</v>
+        <v>548463</v>
       </c>
       <c r="R3" t="n">
-        <v>6828959</v>
+        <v>6828933</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081035</v>
+        <v>124080625</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -938,16 +947,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -957,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R4" t="n">
-        <v>6828955</v>
+        <v>6829001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +996,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,14 +1019,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080853</v>
+        <v>124080834</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1063,11 +1069,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548478</v>
+        <v>548475</v>
       </c>
       <c r="R5" t="n">
-        <v>6828941</v>
+        <v>6828937</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124080625</v>
+        <v>124081035</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1172,8 +1174,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548416</v>
+        <v>548469</v>
       </c>
       <c r="R6" t="n">
-        <v>6829001</v>
+        <v>6828955</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,11 +1231,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,17 +1249,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124078504</v>
+        <v>124081065</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,26 +1272,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1294,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548404</v>
+        <v>548456</v>
       </c>
       <c r="R7" t="n">
-        <v>6828910</v>
+        <v>6828959</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,11 +1356,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1355,17 +1364,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124080834</v>
+        <v>124081277</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1383,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548475</v>
+        <v>548355</v>
       </c>
       <c r="R8" t="n">
-        <v>6828937</v>
+        <v>6828975</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1463,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081020</v>
+        <v>124078504</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,35 +1497,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548463</v>
+        <v>548404</v>
       </c>
       <c r="R9" t="n">
-        <v>6828933</v>
+        <v>6828910</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,11 +1562,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1582,6 +1572,11 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1590,17 +1585,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081277</v>
+        <v>124080746</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,35 +1604,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1645,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548355</v>
+        <v>548458</v>
       </c>
       <c r="R10" t="n">
-        <v>6828975</v>
+        <v>6828939</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,6 +1688,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230620</v>
+        <v>124229699</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548414</v>
+        <v>548469</v>
       </c>
       <c r="R11" t="n">
-        <v>6828951</v>
+        <v>6828940</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,11 +1799,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124229699</v>
+        <v>124230968</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548469</v>
+        <v>548416</v>
       </c>
       <c r="R13" t="n">
-        <v>6828940</v>
+        <v>6828945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,6 +2042,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230968</v>
+        <v>124230620</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548416</v>
+        <v>548414</v>
       </c>
       <c r="R14" t="n">
-        <v>6828945</v>
+        <v>6828951</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124229699</v>
+        <v>124230178</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548469</v>
+        <v>548465</v>
       </c>
       <c r="R11" t="n">
-        <v>6828940</v>
+        <v>6828959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,6 +1799,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230178</v>
+        <v>124230968</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1861,12 +1866,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548465</v>
+        <v>548416</v>
       </c>
       <c r="R12" t="n">
-        <v>6828959</v>
+        <v>6828945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230968</v>
+        <v>124230620</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548416</v>
+        <v>548414</v>
       </c>
       <c r="R13" t="n">
-        <v>6828945</v>
+        <v>6828951</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2051,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230620</v>
+        <v>124229699</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2130,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548414</v>
+        <v>548469</v>
       </c>
       <c r="R14" t="n">
-        <v>6828951</v>
+        <v>6828940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,11 +2171,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230178</v>
+        <v>124230968</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548465</v>
+        <v>548416</v>
       </c>
       <c r="R11" t="n">
-        <v>6828959</v>
+        <v>6828945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1831,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230968</v>
+        <v>124230620</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548416</v>
+        <v>548414</v>
       </c>
       <c r="R12" t="n">
-        <v>6828945</v>
+        <v>6828951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124230620</v>
+        <v>124229699</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548414</v>
+        <v>548469</v>
       </c>
       <c r="R13" t="n">
-        <v>6828951</v>
+        <v>6828940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,11 +2047,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,7 +2074,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124229699</v>
+        <v>124230178</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2114,12 +2109,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2135,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548469</v>
+        <v>548465</v>
       </c>
       <c r="R14" t="n">
-        <v>6828940</v>
+        <v>6828959</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,6 +2166,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080853</v>
+        <v>124078504</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548478</v>
+        <v>548404</v>
       </c>
       <c r="R2" t="n">
-        <v>6828941</v>
+        <v>6828910</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,6 +761,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran rötlåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -787,58 +774,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081020</v>
+        <v>124078022</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548463</v>
+        <v>548372</v>
       </c>
       <c r="R3" t="n">
-        <v>6828933</v>
+        <v>6828876</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,11 +857,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hundratals plantor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +866,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,54 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124080625</v>
+        <v>133403504</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ön 1:1 16, Hls</t>
+          <t>Ön 1:1 Stromorberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548416</v>
+        <v>548471</v>
       </c>
       <c r="R4" t="n">
-        <v>6829001</v>
+        <v>6828944</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,17 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridda inom 5 m2</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +991,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124080834</v>
+        <v>133392000</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,49 +1009,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ön 1:1 16, Hls</t>
+          <t>Ön 1:1 Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548475</v>
+        <v>548520</v>
       </c>
       <c r="R5" t="n">
-        <v>6828937</v>
+        <v>6829013</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,12 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En bål funnen på marken i grandominerad norrsluttning i frivillig avsättning (Kyrkan)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,63 +1100,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124081035</v>
+        <v>124078086</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548469</v>
+        <v>548372</v>
       </c>
       <c r="R6" t="n">
-        <v>6828955</v>
+        <v>6828876</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,13 +1189,17 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,51 +1218,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081065</v>
+        <v>124081277</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548456</v>
+        <v>548355</v>
       </c>
       <c r="R7" t="n">
-        <v>6828959</v>
+        <v>6828975</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1305,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1371,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124081277</v>
+        <v>133403461</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,20 +1356,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ön 1:1 16, Hls</t>
+          <t>Ön 1:1 Stromorberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548355</v>
+        <v>548425</v>
       </c>
       <c r="R8" t="n">
-        <v>6828975</v>
+        <v>6828959</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,12 +1396,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,60 +1421,64 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124078504</v>
+        <v>133396666</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ön 1:1 16, Hls</t>
+          <t>Ön 1:1 Stromorberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548404</v>
+        <v>548488</v>
       </c>
       <c r="R9" t="n">
-        <v>6828910</v>
+        <v>6828949</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,12 +1505,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 fjolårsblomställningar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,11 +1528,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gran rötlåga</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1585,22 +1536,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124080746</v>
+        <v>124080625</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,16 +1571,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1644,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548458</v>
+        <v>548416</v>
       </c>
       <c r="R10" t="n">
-        <v>6828939</v>
+        <v>6829001</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1620,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spridda inom 5 m2</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1700,22 +1643,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230968</v>
+        <v>124080746</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,34 +1680,30 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ön 1:1, Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548416</v>
+        <v>548458</v>
       </c>
       <c r="R11" t="n">
-        <v>6828945</v>
+        <v>6828939</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,11 +1733,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,27 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124230620</v>
+        <v>124080834</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,34 +1790,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ön 1:1, Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548414</v>
+        <v>548475</v>
       </c>
       <c r="R12" t="n">
-        <v>6828951</v>
+        <v>6828937</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1923,11 +1843,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,27 +1858,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124229699</v>
+        <v>124080853</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,34 +1900,34 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ön 1:1, Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548469</v>
+        <v>548478</v>
       </c>
       <c r="R13" t="n">
-        <v>6828940</v>
+        <v>6828941</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2062,27 +1972,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124230178</v>
+        <v>124081020</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,34 +2014,30 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ön 1:1, Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548465</v>
+        <v>548463</v>
       </c>
       <c r="R14" t="n">
-        <v>6828959</v>
+        <v>6828933</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,7 +2071,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Stora mörkgröna blad.</t>
+          <t>hundratals plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,22 +2087,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133403463</v>
+        <v>124081035</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,14 +2142,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stromorberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548425</v>
+        <v>548469</v>
       </c>
       <c r="R15" t="n">
-        <v>6828959</v>
+        <v>6828955</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2275,12 +2176,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,17 +2202,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133391799</v>
+        <v>124081065</v>
       </c>
       <c r="B16" t="n">
-        <v>99178</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,34 +2239,30 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548487</v>
+        <v>548456</v>
       </c>
       <c r="R16" t="n">
-        <v>6828953</v>
+        <v>6828959</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2389,12 +2286,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,68 +2307,76 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133403461</v>
+        <v>124229699</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stromorberget, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548425</v>
+        <v>548469</v>
       </c>
       <c r="R17" t="n">
-        <v>6828959</v>
+        <v>6828940</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,12 +2400,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,28 +2414,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133391701</v>
+        <v>124229934</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,31 +2463,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stormobeget, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548482</v>
+        <v>548384</v>
       </c>
       <c r="R18" t="n">
-        <v>6828948</v>
+        <v>6828991</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2608,12 +2510,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,56 +2543,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133403546</v>
+        <v>124230178</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stromorberget, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548428</v>
+        <v>548465</v>
       </c>
       <c r="R19" t="n">
-        <v>6829068</v>
+        <v>6828959</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2714,12 +2624,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stora mörkgröna blad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,50 +2643,51 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133396278</v>
+        <v>124230620</v>
       </c>
       <c r="B20" t="n">
-        <v>106307</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2781,25 +2697,29 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stromorberget, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548411</v>
+        <v>548414</v>
       </c>
       <c r="R20" t="n">
-        <v>6829073</v>
+        <v>6828951</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2823,17 +2743,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 i knopp</t>
+          <t>Inom naturvårdsbandning inför avverkning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,22 +2769,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133392545</v>
+        <v>124230968</v>
       </c>
       <c r="B21" t="n">
-        <v>99178</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,27 +2811,31 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ön 1:1 Stormoberget, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548397</v>
+        <v>548416</v>
       </c>
       <c r="R21" t="n">
-        <v>6829058</v>
+        <v>6828945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,12 +2862,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Knärotskolonien finns precis i kanten av en naturvårdsbandning inför avverkning. Inget skydd för dessa knärötter trots bandning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,6 +2897,1352 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133391701</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormobeget, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>548482</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6828948</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133391799</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>548487</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6828953</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133392318</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>548457</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6829066</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133392493</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>548401</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6829067</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133392545</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>548397</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6829058</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133396695</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stromorberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>548488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6828949</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133403463</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stromorberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>548425</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6828959</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124078041</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ön 1:1 16, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>548372</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6828876</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133392408</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>548409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6829094</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På nerfallen grangren</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133403546</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stromorberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>548428</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6829068</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133392349</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stormoberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>548440</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6829073</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133396278</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ön 1:1 Stromorberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>548411</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6829073</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 i knopp</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17701-2025 artfynd.xlsx
+++ b/artfynd/A 17701-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133403504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392408</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078086</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081277</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133403461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133403546</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133396666</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080625</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080746</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080834</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2200,6 +2270,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080853</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081020</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2425,6 +2505,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081035</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2535,6 +2620,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081065</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2649,6 +2739,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229699</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229934</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2878,6 +2978,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230178</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2997,6 +3102,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230620</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3116,6 +3226,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230968</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133391701</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3344,6 +3464,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133391799</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3454,6 +3579,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392318</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3568,6 +3698,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392349</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3682,6 +3817,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392493</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3792,6 +3932,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133392545</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3902,6 +4047,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133396695</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4012,6 +4162,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133403463</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4127,6 +4282,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133396278</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4243,8 +4403,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078041</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>